--- a/assets/templates/formato-inspecciones-general.xlsx
+++ b/assets/templates/formato-inspecciones-general.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\ssomac-app-v11.8.4-fix-excel-inspecciones\ssomac-app-v11.8.4-fix-excel-inspecciones\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB457CD-D1A3-461C-8A5A-291EFAD1001B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A28FED-71FC-40FB-9568-9DE8890F62E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1982,72 +1982,48 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2073,52 +2049,65 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2129,6 +2118,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2816,26 +2816,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="67" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="72" t="s">
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="60"/>
+      <c r="N1" s="66"/>
       <c r="O1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2852,22 +2852,22 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="72" t="s">
+      <c r="A2" s="112"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="60"/>
+      <c r="N2" s="66"/>
       <c r="O2" s="1">
         <v>3</v>
       </c>
@@ -2884,24 +2884,24 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="73" t="s">
+      <c r="A3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="72" t="s">
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="60"/>
+      <c r="N3" s="66"/>
       <c r="O3" s="1">
         <v>5</v>
       </c>
@@ -2918,22 +2918,22 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="72" t="s">
+      <c r="A4" s="114"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="60"/>
+      <c r="N4" s="66"/>
       <c r="O4" s="3">
         <v>45855</v>
       </c>
@@ -2950,31 +2950,31 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="46.5" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="60"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="66"/>
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="60"/>
-      <c r="G5" s="76" t="s">
+      <c r="F5" s="66"/>
+      <c r="G5" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="76" t="s">
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="77"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -2988,29 +2988,29 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="30" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="79"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="104"/>
       <c r="D6" s="5">
         <v>20527775851</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="105" t="s">
         <v>175</v>
       </c>
-      <c r="F6" s="75"/>
-      <c r="G6" s="83" t="s">
+      <c r="F6" s="65"/>
+      <c r="G6" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="82"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="108"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -3030,19 +3030,19 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="84" t="s">
+      <c r="G7" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="85"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="84" t="s">
+      <c r="H7" s="93"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="86"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="94"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -3056,27 +3056,27 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="33.75" customHeight="1">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="89" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="90"/>
+      <c r="H8" s="98"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="91" t="s">
+      <c r="J8" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="92"/>
-      <c r="N8" s="92"/>
-      <c r="O8" s="90"/>
+      <c r="K8" s="100"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
+      <c r="N8" s="100"/>
+      <c r="O8" s="98"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -3090,27 +3090,27 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="33.75" customHeight="1">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="95" t="s">
+      <c r="B9" s="66"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="96"/>
+      <c r="H9" s="84"/>
       <c r="I9" s="10"/>
-      <c r="J9" s="97" t="s">
+      <c r="J9" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="98"/>
-      <c r="N9" s="98"/>
-      <c r="O9" s="96"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="86"/>
+      <c r="N9" s="86"/>
+      <c r="O9" s="84"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -3124,29 +3124,29 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="33" customHeight="1">
-      <c r="A10" s="93" t="s">
+      <c r="A10" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="66"/>
       <c r="C10" s="11"/>
       <c r="D10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="100" t="s">
+      <c r="E10" s="87"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="101"/>
+      <c r="H10" s="89"/>
       <c r="I10" s="13"/>
-      <c r="J10" s="102" t="s">
+      <c r="J10" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="103"/>
-      <c r="L10" s="103"/>
-      <c r="M10" s="103"/>
-      <c r="N10" s="103"/>
-      <c r="O10" s="101"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="89"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -3190,39 +3190,39 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="29.25" customHeight="1">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="106" t="s">
+      <c r="B12" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="108" t="s">
+      <c r="C12" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="108" t="s">
+      <c r="D12" s="66"/>
+      <c r="E12" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="60"/>
-      <c r="G12" s="106" t="s">
+      <c r="F12" s="66"/>
+      <c r="G12" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="109" t="s">
+      <c r="H12" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="69"/>
-      <c r="J12" s="106" t="s">
+      <c r="I12" s="71"/>
+      <c r="J12" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="106" t="s">
+      <c r="K12" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="108" t="s">
+      <c r="L12" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="75"/>
-      <c r="N12" s="60"/>
-      <c r="O12" s="110" t="s">
+      <c r="M12" s="65"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="77" t="s">
         <v>37</v>
       </c>
       <c r="P12" s="2"/>
@@ -3238,8 +3238,8 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="25.5" customHeight="1">
-      <c r="A13" s="105"/>
-      <c r="B13" s="107"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="75"/>
       <c r="C13" s="20" t="s">
         <v>38</v>
       </c>
@@ -3252,11 +3252,11 @@
       <c r="F13" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="107"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="107"/>
-      <c r="K13" s="107"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
       <c r="L13" s="21" t="s">
         <v>42</v>
       </c>
@@ -3266,7 +3266,7 @@
       <c r="N13" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="O13" s="111"/>
+      <c r="O13" s="78"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -3289,17 +3289,14 @@
       <c r="E14" s="23"/>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="60"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="66"/>
       <c r="J14" s="26"/>
       <c r="K14" s="27"/>
-      <c r="L14" s="112"/>
-      <c r="M14" s="75"/>
-      <c r="N14" s="60"/>
-      <c r="O14" s="28" t="str">
-        <f t="shared" ref="O14:O23" si="0">IF(L14="A",$C$10+1,IF(L14="B",$C$10+3,IF(L14="C",$C$10+7," ")))</f>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L14" s="64"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="28"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -3322,17 +3319,14 @@
       <c r="E15" s="23"/>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="60"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="66"/>
       <c r="J15" s="26"/>
       <c r="K15" s="27"/>
-      <c r="L15" s="112"/>
-      <c r="M15" s="75"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L15" s="64"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="28"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -3355,17 +3349,14 @@
       <c r="E16" s="23"/>
       <c r="F16" s="25"/>
       <c r="G16" s="16"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="60"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="66"/>
       <c r="J16" s="26"/>
       <c r="K16" s="27"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="75"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L16" s="64"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="28"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3388,17 +3379,14 @@
       <c r="E17" s="23"/>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="60"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="66"/>
       <c r="J17" s="26"/>
       <c r="K17" s="27"/>
-      <c r="L17" s="112"/>
-      <c r="M17" s="75"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L17" s="64"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="28"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3421,17 +3409,14 @@
       <c r="E18" s="23"/>
       <c r="F18" s="29"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="60"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="66"/>
       <c r="J18" s="26"/>
       <c r="K18" s="27"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="75"/>
-      <c r="N18" s="60"/>
-      <c r="O18" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L18" s="64"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="28"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="16"/>
       <c r="R18" s="16"/>
@@ -3454,17 +3439,14 @@
       <c r="E19" s="23"/>
       <c r="F19" s="16"/>
       <c r="G19" s="25"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="60"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="66"/>
       <c r="J19" s="16"/>
       <c r="K19" s="27"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="75"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L19" s="64"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="28"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="16"/>
       <c r="R19" s="2"/>
@@ -3487,17 +3469,14 @@
       <c r="E20" s="23"/>
       <c r="F20" s="29"/>
       <c r="G20" s="25"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="60"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="66"/>
       <c r="J20" s="25"/>
       <c r="K20" s="27"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="75"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L20" s="64"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="28"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="16"/>
       <c r="R20" s="2"/>
@@ -3520,17 +3499,14 @@
       <c r="E21" s="23"/>
       <c r="F21" s="29"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="60"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="66"/>
       <c r="J21" s="25"/>
       <c r="K21" s="23"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="75"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L21" s="64"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="28"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="2"/>
@@ -3553,17 +3529,14 @@
       <c r="E22" s="23"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="60"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="66"/>
       <c r="J22" s="16"/>
       <c r="K22" s="27"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="75"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L22" s="64"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="28"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -3586,17 +3559,14 @@
       <c r="E23" s="23"/>
       <c r="F23" s="16"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="60"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="66"/>
       <c r="J23" s="25"/>
       <c r="K23" s="27"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="75"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
+      <c r="L23" s="64"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="28"/>
       <c r="P23" s="16"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -3610,23 +3580,23 @@
       <c r="Z23" s="2"/>
     </row>
     <row r="24" spans="1:26" ht="24" customHeight="1">
-      <c r="A24" s="113" t="s">
+      <c r="A24" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="75"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="75"/>
-      <c r="O24" s="77"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="68"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
@@ -3644,21 +3614,21 @@
         <v>46</v>
       </c>
       <c r="B25" s="32"/>
-      <c r="C25" s="114"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="114" t="s">
+      <c r="C25" s="69"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="75"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="75"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="77"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="68"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
@@ -3676,21 +3646,21 @@
         <v>48</v>
       </c>
       <c r="B26" s="34"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="116"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="115" t="s">
+      <c r="C26" s="59"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="116"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="116"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="116"/>
-      <c r="M26" s="116"/>
-      <c r="N26" s="116"/>
-      <c r="O26" s="117"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="61"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
@@ -3738,13 +3708,13 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="119"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="63"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -30977,6 +30947,61 @@
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:L2"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="C3:L4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="J9:O9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="J10:O10"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:O25"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="F26:O26"/>
     <mergeCell ref="G28:M28"/>
@@ -30987,61 +31012,6 @@
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="F25:O25"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:O13"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="J9:O9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="J10:O10"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:L2"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="C3:L4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H20:I20"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I10">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="X">
@@ -31067,36 +31037,6 @@
   <pageMargins left="0.27559055118110237" right="0" top="0.15748031496062992" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>'TABLA DE CAUSAS'!$C$3:$C$21</xm:f>
-          </x14:formula1>
-          <xm:sqref>D14:D23</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
-          <x14:formula1>
-            <xm:f>'TABLA DE CAUSAS'!$A$3:$A$22</xm:f>
-          </x14:formula1>
-          <xm:sqref>C14:C18 C21:C23</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
-          <x14:formula1>
-            <xm:f>'TABLA DE CAUSAS'!$B$26:$B$62</xm:f>
-          </x14:formula1>
-          <xm:sqref>F14:F23</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
-          <x14:formula1>
-            <xm:f>'TABLA DE CAUSAS'!$D$26:$D$59</xm:f>
-          </x14:formula1>
-          <xm:sqref>E14:E23</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -31113,12 +31053,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21" customHeight="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="60"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="66"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -31143,14 +31083,14 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="121" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="126" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="121" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="127"/>
+      <c r="D2" s="122"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -31841,12 +31781,12 @@
       <c r="Z23" s="2"/>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1">
-      <c r="A24" s="125" t="s">
+      <c r="A24" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="60"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="66"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -31903,13 +31843,13 @@
       <c r="Z25" s="2"/>
     </row>
     <row r="26" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A26" s="128" t="s">
+      <c r="A26" s="123" t="s">
         <v>93</v>
       </c>
       <c r="B26" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="120" t="s">
+      <c r="C26" s="125" t="s">
         <v>95</v>
       </c>
       <c r="D26" s="52" t="s">
@@ -31939,11 +31879,11 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A27" s="121"/>
+      <c r="A27" s="124"/>
       <c r="B27" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="121"/>
+      <c r="C27" s="124"/>
       <c r="D27" s="53" t="s">
         <v>98</v>
       </c>
@@ -31971,11 +31911,11 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A28" s="121"/>
+      <c r="A28" s="124"/>
       <c r="B28" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="121"/>
+      <c r="C28" s="124"/>
       <c r="D28" s="53" t="s">
         <v>100</v>
       </c>
@@ -32003,11 +31943,11 @@
       <c r="Z28" s="2"/>
     </row>
     <row r="29" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A29" s="121"/>
+      <c r="A29" s="124"/>
       <c r="B29" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="121"/>
+      <c r="C29" s="124"/>
       <c r="D29" s="53" t="s">
         <v>102</v>
       </c>
@@ -32035,11 +31975,11 @@
       <c r="Z29" s="2"/>
     </row>
     <row r="30" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A30" s="121"/>
+      <c r="A30" s="124"/>
       <c r="B30" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="107"/>
+      <c r="C30" s="75"/>
       <c r="D30" s="54" t="s">
         <v>104</v>
       </c>
@@ -32067,11 +32007,11 @@
       <c r="Z30" s="2"/>
     </row>
     <row r="31" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A31" s="121"/>
+      <c r="A31" s="124"/>
       <c r="B31" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="120" t="s">
+      <c r="C31" s="125" t="s">
         <v>106</v>
       </c>
       <c r="D31" s="52" t="s">
@@ -32101,11 +32041,11 @@
       <c r="Z31" s="2"/>
     </row>
     <row r="32" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A32" s="121"/>
+      <c r="A32" s="124"/>
       <c r="B32" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="121"/>
+      <c r="C32" s="124"/>
       <c r="D32" s="53" t="s">
         <v>109</v>
       </c>
@@ -32133,11 +32073,11 @@
       <c r="Z32" s="2"/>
     </row>
     <row r="33" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A33" s="121"/>
+      <c r="A33" s="124"/>
       <c r="B33" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="121"/>
+      <c r="C33" s="124"/>
       <c r="D33" s="53" t="s">
         <v>111</v>
       </c>
@@ -32165,11 +32105,11 @@
       <c r="Z33" s="2"/>
     </row>
     <row r="34" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A34" s="121"/>
+      <c r="A34" s="124"/>
       <c r="B34" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="121"/>
+      <c r="C34" s="124"/>
       <c r="D34" s="53" t="s">
         <v>113</v>
       </c>
@@ -32197,11 +32137,11 @@
       <c r="Z34" s="2"/>
     </row>
     <row r="35" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A35" s="121"/>
+      <c r="A35" s="124"/>
       <c r="B35" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="121"/>
+      <c r="C35" s="124"/>
       <c r="D35" s="53" t="s">
         <v>115</v>
       </c>
@@ -32229,11 +32169,11 @@
       <c r="Z35" s="2"/>
     </row>
     <row r="36" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A36" s="107"/>
+      <c r="A36" s="75"/>
       <c r="B36" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="121"/>
+      <c r="C36" s="124"/>
       <c r="D36" s="53" t="s">
         <v>117</v>
       </c>
@@ -32261,13 +32201,13 @@
       <c r="Z36" s="2"/>
     </row>
     <row r="37" spans="1:26" ht="28.5" customHeight="1">
-      <c r="A37" s="128" t="s">
+      <c r="A37" s="123" t="s">
         <v>118</v>
       </c>
       <c r="B37" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="121"/>
+      <c r="C37" s="124"/>
       <c r="D37" s="53" t="s">
         <v>120</v>
       </c>
@@ -32295,11 +32235,11 @@
       <c r="Z37" s="2"/>
     </row>
     <row r="38" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A38" s="121"/>
+      <c r="A38" s="124"/>
       <c r="B38" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="C38" s="121"/>
+      <c r="C38" s="124"/>
       <c r="D38" s="53" t="s">
         <v>122</v>
       </c>
@@ -32327,11 +32267,11 @@
       <c r="Z38" s="2"/>
     </row>
     <row r="39" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A39" s="121"/>
+      <c r="A39" s="124"/>
       <c r="B39" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="121"/>
+      <c r="C39" s="124"/>
       <c r="D39" s="54" t="s">
         <v>124</v>
       </c>
@@ -32359,11 +32299,11 @@
       <c r="Z39" s="2"/>
     </row>
     <row r="40" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A40" s="121"/>
+      <c r="A40" s="124"/>
       <c r="B40" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="C40" s="121"/>
+      <c r="C40" s="124"/>
       <c r="D40" s="53" t="s">
         <v>126</v>
       </c>
@@ -32391,11 +32331,11 @@
       <c r="Z40" s="2"/>
     </row>
     <row r="41" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A41" s="121"/>
+      <c r="A41" s="124"/>
       <c r="B41" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="107"/>
+      <c r="C41" s="75"/>
       <c r="D41" s="52" t="s">
         <v>128</v>
       </c>
@@ -32423,11 +32363,11 @@
       <c r="Z41" s="2"/>
     </row>
     <row r="42" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A42" s="121"/>
+      <c r="A42" s="124"/>
       <c r="B42" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="C42" s="122" t="s">
+      <c r="C42" s="126" t="s">
         <v>130</v>
       </c>
       <c r="D42" s="53" t="s">
@@ -32457,11 +32397,11 @@
       <c r="Z42" s="2"/>
     </row>
     <row r="43" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A43" s="121"/>
+      <c r="A43" s="124"/>
       <c r="B43" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="C43" s="111"/>
+      <c r="C43" s="78"/>
       <c r="D43" s="53" t="s">
         <v>133</v>
       </c>
@@ -32489,11 +32429,11 @@
       <c r="Z43" s="2"/>
     </row>
     <row r="44" spans="1:26" ht="63" customHeight="1">
-      <c r="A44" s="121"/>
+      <c r="A44" s="124"/>
       <c r="B44" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="122" t="s">
+      <c r="C44" s="126" t="s">
         <v>135</v>
       </c>
       <c r="D44" s="53" t="s">
@@ -32523,11 +32463,11 @@
       <c r="Z44" s="2"/>
     </row>
     <row r="45" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A45" s="121"/>
+      <c r="A45" s="124"/>
       <c r="B45" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="123"/>
+      <c r="C45" s="127"/>
       <c r="D45" s="53" t="s">
         <v>138</v>
       </c>
@@ -32555,11 +32495,11 @@
       <c r="Z45" s="2"/>
     </row>
     <row r="46" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A46" s="121"/>
+      <c r="A46" s="124"/>
       <c r="B46" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="C46" s="123"/>
+      <c r="C46" s="127"/>
       <c r="D46" s="53" t="s">
         <v>140</v>
       </c>
@@ -32587,11 +32527,11 @@
       <c r="Z46" s="2"/>
     </row>
     <row r="47" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A47" s="107"/>
+      <c r="A47" s="75"/>
       <c r="B47" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="123"/>
+      <c r="C47" s="127"/>
       <c r="D47" s="54" t="s">
         <v>142</v>
       </c>
@@ -32619,13 +32559,13 @@
       <c r="Z47" s="2"/>
     </row>
     <row r="48" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A48" s="124" t="s">
+      <c r="A48" s="128" t="s">
         <v>143</v>
       </c>
       <c r="B48" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="C48" s="123"/>
+      <c r="C48" s="127"/>
       <c r="D48" s="52" t="s">
         <v>145</v>
       </c>
@@ -32653,11 +32593,11 @@
       <c r="Z48" s="2"/>
     </row>
     <row r="49" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A49" s="121"/>
+      <c r="A49" s="124"/>
       <c r="B49" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="C49" s="123"/>
+      <c r="C49" s="127"/>
       <c r="D49" s="53" t="s">
         <v>147</v>
       </c>
@@ -32685,11 +32625,11 @@
       <c r="Z49" s="2"/>
     </row>
     <row r="50" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A50" s="121"/>
+      <c r="A50" s="124"/>
       <c r="B50" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="C50" s="111"/>
+      <c r="C50" s="78"/>
       <c r="D50" s="54" t="s">
         <v>149</v>
       </c>
@@ -32717,11 +32657,11 @@
       <c r="Z50" s="2"/>
     </row>
     <row r="51" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A51" s="121"/>
+      <c r="A51" s="124"/>
       <c r="B51" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="C51" s="122" t="s">
+      <c r="C51" s="126" t="s">
         <v>151</v>
       </c>
       <c r="D51" s="52" t="s">
@@ -32751,11 +32691,11 @@
       <c r="Z51" s="2"/>
     </row>
     <row r="52" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A52" s="121"/>
+      <c r="A52" s="124"/>
       <c r="B52" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="C52" s="123"/>
+      <c r="C52" s="127"/>
       <c r="D52" s="53" t="s">
         <v>154</v>
       </c>
@@ -32783,11 +32723,11 @@
       <c r="Z52" s="2"/>
     </row>
     <row r="53" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A53" s="121"/>
+      <c r="A53" s="124"/>
       <c r="B53" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="C53" s="111"/>
+      <c r="C53" s="78"/>
       <c r="D53" s="53" t="s">
         <v>156</v>
       </c>
@@ -32815,11 +32755,11 @@
       <c r="Z53" s="2"/>
     </row>
     <row r="54" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A54" s="121"/>
+      <c r="A54" s="124"/>
       <c r="B54" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="122" t="s">
+      <c r="C54" s="126" t="s">
         <v>158</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -32849,11 +32789,11 @@
       <c r="Z54" s="2"/>
     </row>
     <row r="55" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A55" s="121"/>
+      <c r="A55" s="124"/>
       <c r="B55" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="C55" s="123"/>
+      <c r="C55" s="127"/>
       <c r="D55" s="53" t="s">
         <v>161</v>
       </c>
@@ -32881,11 +32821,11 @@
       <c r="Z55" s="2"/>
     </row>
     <row r="56" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A56" s="121"/>
+      <c r="A56" s="124"/>
       <c r="B56" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="C56" s="123"/>
+      <c r="C56" s="127"/>
       <c r="D56" s="53" t="s">
         <v>163</v>
       </c>
@@ -32913,11 +32853,11 @@
       <c r="Z56" s="2"/>
     </row>
     <row r="57" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A57" s="121"/>
+      <c r="A57" s="124"/>
       <c r="B57" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="C57" s="123"/>
+      <c r="C57" s="127"/>
       <c r="D57" s="54" t="s">
         <v>165</v>
       </c>
@@ -32945,11 +32885,11 @@
       <c r="Z57" s="2"/>
     </row>
     <row r="58" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A58" s="107"/>
+      <c r="A58" s="75"/>
       <c r="B58" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="C58" s="123"/>
+      <c r="C58" s="127"/>
       <c r="D58" s="52" t="s">
         <v>167</v>
       </c>
@@ -32977,13 +32917,13 @@
       <c r="Z58" s="2"/>
     </row>
     <row r="59" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A59" s="122" t="s">
+      <c r="A59" s="126" t="s">
         <v>168</v>
       </c>
       <c r="B59" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="C59" s="123"/>
+      <c r="C59" s="127"/>
       <c r="D59" s="54" t="s">
         <v>170</v>
       </c>
@@ -33011,11 +32951,11 @@
       <c r="Z59" s="2"/>
     </row>
     <row r="60" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A60" s="123"/>
+      <c r="A60" s="127"/>
       <c r="B60" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="C60" s="111"/>
+      <c r="C60" s="78"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -33041,11 +32981,11 @@
       <c r="Z60" s="2"/>
     </row>
     <row r="61" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A61" s="123"/>
+      <c r="A61" s="127"/>
       <c r="B61" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="C61" s="122" t="s">
+      <c r="C61" s="126" t="s">
         <v>173</v>
       </c>
       <c r="D61" s="2"/>
@@ -33073,11 +33013,11 @@
       <c r="Z61" s="2"/>
     </row>
     <row r="62" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A62" s="123"/>
+      <c r="A62" s="127"/>
       <c r="B62" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="C62" s="111"/>
+      <c r="C62" s="78"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
@@ -59368,13 +59308,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A26:A36"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="C31:C41"/>
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="C44:C50"/>
     <mergeCell ref="A48:A58"/>
@@ -59383,6 +59316,13 @@
     <mergeCell ref="A59:A62"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="A37:A47"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A26:A36"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C31:C41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/assets/templates/formato-inspecciones-general.xlsx
+++ b/assets/templates/formato-inspecciones-general.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\ssomac-app-v11.8.4-fix-excel-inspecciones\ssomac-app-v11.8.4-fix-excel-inspecciones\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A28FED-71FC-40FB-9568-9DE8890F62E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB457CD-D1A3-461C-8A5A-291EFAD1001B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1982,48 +1982,72 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2049,65 +2073,52 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2118,17 +2129,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2816,26 +2816,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="115" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="117" t="s">
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="66"/>
+      <c r="N1" s="60"/>
       <c r="O1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2852,22 +2852,22 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" s="112"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="117" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="66"/>
+      <c r="N2" s="60"/>
       <c r="O2" s="1">
         <v>3</v>
       </c>
@@ -2884,24 +2884,24 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A3" s="112"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="118" t="s">
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="117" t="s">
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="66"/>
+      <c r="N3" s="60"/>
       <c r="O3" s="1">
         <v>5</v>
       </c>
@@ -2918,22 +2918,22 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="117" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="66"/>
+      <c r="N4" s="60"/>
       <c r="O4" s="3">
         <v>45855</v>
       </c>
@@ -2950,31 +2950,31 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="46.5" customHeight="1">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="60"/>
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E5" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="102" t="s">
+      <c r="F5" s="60"/>
+      <c r="G5" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="102" t="s">
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="68"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="77"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -2988,29 +2988,29 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="30" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="104"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="79"/>
       <c r="D6" s="5">
         <v>20527775851</v>
       </c>
-      <c r="E6" s="105" t="s">
+      <c r="E6" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="F6" s="65"/>
-      <c r="G6" s="109" t="s">
+      <c r="F6" s="75"/>
+      <c r="G6" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="107"/>
-      <c r="N6" s="107"/>
-      <c r="O6" s="108"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="82"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -3030,19 +3030,19 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="92" t="s">
+      <c r="G7" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="93"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="92" t="s">
+      <c r="H7" s="85"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="94"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="86"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -3056,27 +3056,27 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="33.75" customHeight="1">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="97" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="98"/>
+      <c r="H8" s="90"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="99" t="s">
+      <c r="J8" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="100"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="100"/>
-      <c r="N8" s="100"/>
-      <c r="O8" s="98"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="92"/>
+      <c r="M8" s="92"/>
+      <c r="N8" s="92"/>
+      <c r="O8" s="90"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -3090,27 +3090,27 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="33.75" customHeight="1">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="83" t="s">
+      <c r="B9" s="60"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="84"/>
+      <c r="H9" s="96"/>
       <c r="I9" s="10"/>
-      <c r="J9" s="85" t="s">
+      <c r="J9" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="86"/>
-      <c r="N9" s="86"/>
-      <c r="O9" s="84"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="98"/>
+      <c r="N9" s="98"/>
+      <c r="O9" s="96"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -3124,29 +3124,29 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="33" customHeight="1">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="66"/>
+      <c r="B10" s="60"/>
       <c r="C10" s="11"/>
       <c r="D10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="88" t="s">
+      <c r="E10" s="99"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="89"/>
+      <c r="H10" s="101"/>
       <c r="I10" s="13"/>
-      <c r="J10" s="90" t="s">
+      <c r="J10" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="89"/>
+      <c r="K10" s="103"/>
+      <c r="L10" s="103"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="103"/>
+      <c r="O10" s="101"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -3190,39 +3190,39 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="29.25" customHeight="1">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="66"/>
-      <c r="E12" s="76" t="s">
+      <c r="D12" s="60"/>
+      <c r="E12" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="66"/>
-      <c r="G12" s="74" t="s">
+      <c r="F12" s="60"/>
+      <c r="G12" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="70" t="s">
+      <c r="H12" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="71"/>
-      <c r="J12" s="74" t="s">
+      <c r="I12" s="69"/>
+      <c r="J12" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="74" t="s">
+      <c r="K12" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="76" t="s">
+      <c r="L12" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="65"/>
-      <c r="N12" s="66"/>
-      <c r="O12" s="77" t="s">
+      <c r="M12" s="75"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="110" t="s">
         <v>37</v>
       </c>
       <c r="P12" s="2"/>
@@ -3238,8 +3238,8 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="25.5" customHeight="1">
-      <c r="A13" s="80"/>
-      <c r="B13" s="75"/>
+      <c r="A13" s="105"/>
+      <c r="B13" s="107"/>
       <c r="C13" s="20" t="s">
         <v>38</v>
       </c>
@@ -3252,11 +3252,11 @@
       <c r="F13" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="75"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="107"/>
       <c r="L13" s="21" t="s">
         <v>42</v>
       </c>
@@ -3266,7 +3266,7 @@
       <c r="N13" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="O13" s="78"/>
+      <c r="O13" s="111"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -3289,14 +3289,16 @@
       <c r="E14" s="23"/>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="66"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="60"/>
       <c r="J14" s="26"/>
       <c r="K14" s="27"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="66"/>
-      <c r="O14" s="28"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="75"/>
+      <c r="N14" s="60"/>
+      <c r="O14" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -3319,14 +3321,16 @@
       <c r="E15" s="23"/>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="66"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="60"/>
       <c r="J15" s="26"/>
       <c r="K15" s="27"/>
-      <c r="L15" s="64"/>
-      <c r="M15" s="65"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="28"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="75"/>
+      <c r="N15" s="60"/>
+      <c r="O15" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -3349,14 +3353,16 @@
       <c r="E16" s="23"/>
       <c r="F16" s="25"/>
       <c r="G16" s="16"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="66"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="60"/>
       <c r="J16" s="26"/>
       <c r="K16" s="27"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="65"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="28"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3379,14 +3385,16 @@
       <c r="E17" s="23"/>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="66"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="60"/>
       <c r="J17" s="26"/>
       <c r="K17" s="27"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="65"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="28"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="75"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3409,14 +3417,16 @@
       <c r="E18" s="23"/>
       <c r="F18" s="29"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="66"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="60"/>
       <c r="J18" s="26"/>
       <c r="K18" s="27"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="65"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="28"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="16"/>
       <c r="R18" s="16"/>
@@ -3439,14 +3449,16 @@
       <c r="E19" s="23"/>
       <c r="F19" s="16"/>
       <c r="G19" s="25"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="66"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="60"/>
       <c r="J19" s="16"/>
       <c r="K19" s="27"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="28"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="75"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="16"/>
       <c r="R19" s="2"/>
@@ -3469,14 +3481,16 @@
       <c r="E20" s="23"/>
       <c r="F20" s="29"/>
       <c r="G20" s="25"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="66"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="60"/>
       <c r="J20" s="25"/>
       <c r="K20" s="27"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="65"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="28"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="75"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P20" s="2"/>
       <c r="Q20" s="16"/>
       <c r="R20" s="2"/>
@@ -3499,14 +3513,16 @@
       <c r="E21" s="23"/>
       <c r="F21" s="29"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="66"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="60"/>
       <c r="J21" s="25"/>
       <c r="K21" s="23"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="28"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="75"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="2"/>
@@ -3529,14 +3545,16 @@
       <c r="E22" s="23"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="66"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="60"/>
       <c r="J22" s="16"/>
       <c r="K22" s="27"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="28"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -3559,14 +3577,16 @@
       <c r="E23" s="23"/>
       <c r="F23" s="16"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="66"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="60"/>
       <c r="J23" s="25"/>
       <c r="K23" s="27"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="28"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="75"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="28" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="P23" s="16"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -3580,23 +3600,23 @@
       <c r="Z23" s="2"/>
     </row>
     <row r="24" spans="1:26" ht="24" customHeight="1">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="65"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="68"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="77"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
@@ -3614,21 +3634,21 @@
         <v>46</v>
       </c>
       <c r="B25" s="32"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="69" t="s">
+      <c r="C25" s="114"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="65"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="68"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="77"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
@@ -3646,21 +3666,21 @@
         <v>48</v>
       </c>
       <c r="B26" s="34"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="59" t="s">
+      <c r="C26" s="115"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="60"/>
-      <c r="N26" s="60"/>
-      <c r="O26" s="61"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="116"/>
+      <c r="M26" s="116"/>
+      <c r="N26" s="116"/>
+      <c r="O26" s="117"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
@@ -3708,13 +3728,13 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="63"/>
-      <c r="M28" s="63"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="119"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -30947,13 +30967,46 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:L2"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="C3:L4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:O26"/>
+    <mergeCell ref="G28:M28"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:O25"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="J9:O9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="J10:O10"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="J8:O8"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:J5"/>
@@ -30962,36 +31015,13 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="K6:O6"/>
     <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="J9:O9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="J10:O10"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:O13"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="F25:O25"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:L2"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="C3:L4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H22:I22"/>
     <mergeCell ref="H23:I23"/>
@@ -31002,16 +31032,6 @@
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="H20:I20"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:O26"/>
-    <mergeCell ref="G28:M28"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I10">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="X">
@@ -31037,6 +31057,36 @@
   <pageMargins left="0.27559055118110237" right="0" top="0.15748031496062992" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>'TABLA DE CAUSAS'!$C$3:$C$21</xm:f>
+          </x14:formula1>
+          <xm:sqref>D14:D23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>'TABLA DE CAUSAS'!$A$3:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>C14:C18 C21:C23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+          <x14:formula1>
+            <xm:f>'TABLA DE CAUSAS'!$B$26:$B$62</xm:f>
+          </x14:formula1>
+          <xm:sqref>F14:F23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
+          <x14:formula1>
+            <xm:f>'TABLA DE CAUSAS'!$D$26:$D$59</xm:f>
+          </x14:formula1>
+          <xm:sqref>E14:E23</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -31053,12 +31103,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="125" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="66"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="60"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -31083,14 +31133,14 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="126" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="121" t="s">
+      <c r="B2" s="127"/>
+      <c r="C2" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="122"/>
+      <c r="D2" s="127"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -31781,12 +31831,12 @@
       <c r="Z23" s="2"/>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="65"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="66"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="60"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -31843,13 +31893,13 @@
       <c r="Z25" s="2"/>
     </row>
     <row r="26" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A26" s="123" t="s">
+      <c r="A26" s="128" t="s">
         <v>93</v>
       </c>
       <c r="B26" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="125" t="s">
+      <c r="C26" s="120" t="s">
         <v>95</v>
       </c>
       <c r="D26" s="52" t="s">
@@ -31879,11 +31929,11 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A27" s="124"/>
+      <c r="A27" s="121"/>
       <c r="B27" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="124"/>
+      <c r="C27" s="121"/>
       <c r="D27" s="53" t="s">
         <v>98</v>
       </c>
@@ -31911,11 +31961,11 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A28" s="124"/>
+      <c r="A28" s="121"/>
       <c r="B28" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="124"/>
+      <c r="C28" s="121"/>
       <c r="D28" s="53" t="s">
         <v>100</v>
       </c>
@@ -31943,11 +31993,11 @@
       <c r="Z28" s="2"/>
     </row>
     <row r="29" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A29" s="124"/>
+      <c r="A29" s="121"/>
       <c r="B29" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="124"/>
+      <c r="C29" s="121"/>
       <c r="D29" s="53" t="s">
         <v>102</v>
       </c>
@@ -31975,11 +32025,11 @@
       <c r="Z29" s="2"/>
     </row>
     <row r="30" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A30" s="124"/>
+      <c r="A30" s="121"/>
       <c r="B30" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="75"/>
+      <c r="C30" s="107"/>
       <c r="D30" s="54" t="s">
         <v>104</v>
       </c>
@@ -32007,11 +32057,11 @@
       <c r="Z30" s="2"/>
     </row>
     <row r="31" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A31" s="124"/>
+      <c r="A31" s="121"/>
       <c r="B31" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="125" t="s">
+      <c r="C31" s="120" t="s">
         <v>106</v>
       </c>
       <c r="D31" s="52" t="s">
@@ -32041,11 +32091,11 @@
       <c r="Z31" s="2"/>
     </row>
     <row r="32" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A32" s="124"/>
+      <c r="A32" s="121"/>
       <c r="B32" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="124"/>
+      <c r="C32" s="121"/>
       <c r="D32" s="53" t="s">
         <v>109</v>
       </c>
@@ -32073,11 +32123,11 @@
       <c r="Z32" s="2"/>
     </row>
     <row r="33" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A33" s="124"/>
+      <c r="A33" s="121"/>
       <c r="B33" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="124"/>
+      <c r="C33" s="121"/>
       <c r="D33" s="53" t="s">
         <v>111</v>
       </c>
@@ -32105,11 +32155,11 @@
       <c r="Z33" s="2"/>
     </row>
     <row r="34" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A34" s="124"/>
+      <c r="A34" s="121"/>
       <c r="B34" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="124"/>
+      <c r="C34" s="121"/>
       <c r="D34" s="53" t="s">
         <v>113</v>
       </c>
@@ -32137,11 +32187,11 @@
       <c r="Z34" s="2"/>
     </row>
     <row r="35" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A35" s="124"/>
+      <c r="A35" s="121"/>
       <c r="B35" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="124"/>
+      <c r="C35" s="121"/>
       <c r="D35" s="53" t="s">
         <v>115</v>
       </c>
@@ -32169,11 +32219,11 @@
       <c r="Z35" s="2"/>
     </row>
     <row r="36" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A36" s="75"/>
+      <c r="A36" s="107"/>
       <c r="B36" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="124"/>
+      <c r="C36" s="121"/>
       <c r="D36" s="53" t="s">
         <v>117</v>
       </c>
@@ -32201,13 +32251,13 @@
       <c r="Z36" s="2"/>
     </row>
     <row r="37" spans="1:26" ht="28.5" customHeight="1">
-      <c r="A37" s="123" t="s">
+      <c r="A37" s="128" t="s">
         <v>118</v>
       </c>
       <c r="B37" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="124"/>
+      <c r="C37" s="121"/>
       <c r="D37" s="53" t="s">
         <v>120</v>
       </c>
@@ -32235,11 +32285,11 @@
       <c r="Z37" s="2"/>
     </row>
     <row r="38" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A38" s="124"/>
+      <c r="A38" s="121"/>
       <c r="B38" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="C38" s="124"/>
+      <c r="C38" s="121"/>
       <c r="D38" s="53" t="s">
         <v>122</v>
       </c>
@@ -32267,11 +32317,11 @@
       <c r="Z38" s="2"/>
     </row>
     <row r="39" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A39" s="124"/>
+      <c r="A39" s="121"/>
       <c r="B39" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="124"/>
+      <c r="C39" s="121"/>
       <c r="D39" s="54" t="s">
         <v>124</v>
       </c>
@@ -32299,11 +32349,11 @@
       <c r="Z39" s="2"/>
     </row>
     <row r="40" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A40" s="124"/>
+      <c r="A40" s="121"/>
       <c r="B40" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="C40" s="124"/>
+      <c r="C40" s="121"/>
       <c r="D40" s="53" t="s">
         <v>126</v>
       </c>
@@ -32331,11 +32381,11 @@
       <c r="Z40" s="2"/>
     </row>
     <row r="41" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A41" s="124"/>
+      <c r="A41" s="121"/>
       <c r="B41" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="75"/>
+      <c r="C41" s="107"/>
       <c r="D41" s="52" t="s">
         <v>128</v>
       </c>
@@ -32363,11 +32413,11 @@
       <c r="Z41" s="2"/>
     </row>
     <row r="42" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A42" s="124"/>
+      <c r="A42" s="121"/>
       <c r="B42" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="C42" s="126" t="s">
+      <c r="C42" s="122" t="s">
         <v>130</v>
       </c>
       <c r="D42" s="53" t="s">
@@ -32397,11 +32447,11 @@
       <c r="Z42" s="2"/>
     </row>
     <row r="43" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A43" s="124"/>
+      <c r="A43" s="121"/>
       <c r="B43" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="C43" s="78"/>
+      <c r="C43" s="111"/>
       <c r="D43" s="53" t="s">
         <v>133</v>
       </c>
@@ -32429,11 +32479,11 @@
       <c r="Z43" s="2"/>
     </row>
     <row r="44" spans="1:26" ht="63" customHeight="1">
-      <c r="A44" s="124"/>
+      <c r="A44" s="121"/>
       <c r="B44" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="126" t="s">
+      <c r="C44" s="122" t="s">
         <v>135</v>
       </c>
       <c r="D44" s="53" t="s">
@@ -32463,11 +32513,11 @@
       <c r="Z44" s="2"/>
     </row>
     <row r="45" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A45" s="124"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="127"/>
+      <c r="C45" s="123"/>
       <c r="D45" s="53" t="s">
         <v>138</v>
       </c>
@@ -32495,11 +32545,11 @@
       <c r="Z45" s="2"/>
     </row>
     <row r="46" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A46" s="124"/>
+      <c r="A46" s="121"/>
       <c r="B46" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="C46" s="127"/>
+      <c r="C46" s="123"/>
       <c r="D46" s="53" t="s">
         <v>140</v>
       </c>
@@ -32527,11 +32577,11 @@
       <c r="Z46" s="2"/>
     </row>
     <row r="47" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A47" s="75"/>
+      <c r="A47" s="107"/>
       <c r="B47" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="127"/>
+      <c r="C47" s="123"/>
       <c r="D47" s="54" t="s">
         <v>142</v>
       </c>
@@ -32559,13 +32609,13 @@
       <c r="Z47" s="2"/>
     </row>
     <row r="48" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A48" s="128" t="s">
+      <c r="A48" s="124" t="s">
         <v>143</v>
       </c>
       <c r="B48" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="C48" s="127"/>
+      <c r="C48" s="123"/>
       <c r="D48" s="52" t="s">
         <v>145</v>
       </c>
@@ -32593,11 +32643,11 @@
       <c r="Z48" s="2"/>
     </row>
     <row r="49" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A49" s="124"/>
+      <c r="A49" s="121"/>
       <c r="B49" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="C49" s="127"/>
+      <c r="C49" s="123"/>
       <c r="D49" s="53" t="s">
         <v>147</v>
       </c>
@@ -32625,11 +32675,11 @@
       <c r="Z49" s="2"/>
     </row>
     <row r="50" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A50" s="124"/>
+      <c r="A50" s="121"/>
       <c r="B50" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="C50" s="78"/>
+      <c r="C50" s="111"/>
       <c r="D50" s="54" t="s">
         <v>149</v>
       </c>
@@ -32657,11 +32707,11 @@
       <c r="Z50" s="2"/>
     </row>
     <row r="51" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A51" s="124"/>
+      <c r="A51" s="121"/>
       <c r="B51" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="C51" s="126" t="s">
+      <c r="C51" s="122" t="s">
         <v>151</v>
       </c>
       <c r="D51" s="52" t="s">
@@ -32691,11 +32741,11 @@
       <c r="Z51" s="2"/>
     </row>
     <row r="52" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A52" s="124"/>
+      <c r="A52" s="121"/>
       <c r="B52" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="C52" s="127"/>
+      <c r="C52" s="123"/>
       <c r="D52" s="53" t="s">
         <v>154</v>
       </c>
@@ -32723,11 +32773,11 @@
       <c r="Z52" s="2"/>
     </row>
     <row r="53" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A53" s="124"/>
+      <c r="A53" s="121"/>
       <c r="B53" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="C53" s="78"/>
+      <c r="C53" s="111"/>
       <c r="D53" s="53" t="s">
         <v>156</v>
       </c>
@@ -32755,11 +32805,11 @@
       <c r="Z53" s="2"/>
     </row>
     <row r="54" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A54" s="124"/>
+      <c r="A54" s="121"/>
       <c r="B54" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="126" t="s">
+      <c r="C54" s="122" t="s">
         <v>158</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -32789,11 +32839,11 @@
       <c r="Z54" s="2"/>
     </row>
     <row r="55" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A55" s="124"/>
+      <c r="A55" s="121"/>
       <c r="B55" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="C55" s="127"/>
+      <c r="C55" s="123"/>
       <c r="D55" s="53" t="s">
         <v>161</v>
       </c>
@@ -32821,11 +32871,11 @@
       <c r="Z55" s="2"/>
     </row>
     <row r="56" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A56" s="124"/>
+      <c r="A56" s="121"/>
       <c r="B56" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="C56" s="127"/>
+      <c r="C56" s="123"/>
       <c r="D56" s="53" t="s">
         <v>163</v>
       </c>
@@ -32853,11 +32903,11 @@
       <c r="Z56" s="2"/>
     </row>
     <row r="57" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A57" s="124"/>
+      <c r="A57" s="121"/>
       <c r="B57" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="C57" s="127"/>
+      <c r="C57" s="123"/>
       <c r="D57" s="54" t="s">
         <v>165</v>
       </c>
@@ -32885,11 +32935,11 @@
       <c r="Z57" s="2"/>
     </row>
     <row r="58" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A58" s="75"/>
+      <c r="A58" s="107"/>
       <c r="B58" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="C58" s="127"/>
+      <c r="C58" s="123"/>
       <c r="D58" s="52" t="s">
         <v>167</v>
       </c>
@@ -32917,13 +32967,13 @@
       <c r="Z58" s="2"/>
     </row>
     <row r="59" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A59" s="126" t="s">
+      <c r="A59" s="122" t="s">
         <v>168</v>
       </c>
       <c r="B59" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="C59" s="127"/>
+      <c r="C59" s="123"/>
       <c r="D59" s="54" t="s">
         <v>170</v>
       </c>
@@ -32951,11 +33001,11 @@
       <c r="Z59" s="2"/>
     </row>
     <row r="60" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A60" s="127"/>
+      <c r="A60" s="123"/>
       <c r="B60" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="C60" s="78"/>
+      <c r="C60" s="111"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -32981,11 +33031,11 @@
       <c r="Z60" s="2"/>
     </row>
     <row r="61" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A61" s="127"/>
+      <c r="A61" s="123"/>
       <c r="B61" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="C61" s="126" t="s">
+      <c r="C61" s="122" t="s">
         <v>173</v>
       </c>
       <c r="D61" s="2"/>
@@ -33013,11 +33063,11 @@
       <c r="Z61" s="2"/>
     </row>
     <row r="62" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A62" s="127"/>
+      <c r="A62" s="123"/>
       <c r="B62" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="C62" s="78"/>
+      <c r="C62" s="111"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
@@ -59308,6 +59358,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A26:A36"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C31:C41"/>
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="C44:C50"/>
     <mergeCell ref="A48:A58"/>
@@ -59316,13 +59373,6 @@
     <mergeCell ref="A59:A62"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="A37:A47"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A26:A36"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="C31:C41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
